--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -595,22 +595,26 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ORDERs (odd internal casing) :: ORDERs â€” â€”Continued.</t>
+          <t>L20: suspicious token(s): ORDERs (odd internal casing) :: ORDERs — —Continued.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ORDERSâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 94</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L32: symbol-only separator/garbage line :: . 105</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ORDERs (odd internal casing) :: ORDERs â€” â€”Continued.</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 86â€”87â€”122</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 111</t>
+          <t>L28: symbol-only separator/garbage line :: 86—87—122</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -727,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 105</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: . 111</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,7 +778,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -786,12 +794,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3â€”104</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -803,7 +811,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 94</t>
+          <t>L32: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -843,22 +851,22 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 66â€”67</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 94</t>
+          <t>L34: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -899,11 +907,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 67â€”68</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -913,7 +917,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 138</t>
+          <t>L36: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -954,11 +958,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 111</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 138</t>
+          <t>L38: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1009,11 +1009,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1023,7 +1019,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 146</t>
+          <t>L40: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1049,12 +1045,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1064,11 +1060,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”87</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1078,7 +1070,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L55: symbol-only separator/garbage line :: . 142</t>
+          <t>L46: symbol-only separator/garbage line :: 3—104</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1105,7 +1097,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1115,11 +1107,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 79â€”80â€”81</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1129,7 +1117,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: . 140</t>
+          <t>L48: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1151,12 +1139,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1166,11 +1154,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 82â€”83</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1180,7 +1164,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 114</t>
+          <t>L50: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1217,11 +1201,7 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5â€”6</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1231,7 +1211,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: %</t>
+          <t>L53: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1258,7 +1238,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1278,7 +1258,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 68</t>
+          <t>L55: symbol-only separator/garbage line :: . 142</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1325,7 +1305,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 112</t>
+          <t>L57: symbol-only separator/garbage line :: . 140</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1372,7 +1352,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1419,7 +1399,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 110</t>
+          <t>L65: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1454,7 +1434,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: .3</t>
+          <t>L94: symbol-only separator/garbage line :: 66—67</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1489,7 +1469,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 3-4</t>
+          <t>L95: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1524,7 +1504,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: - 8</t>
+          <t>L97: symbol-only separator/garbage line :: . 67—68</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1559,7 +1539,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 12</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1594,7 +1574,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 155</t>
+          <t>L101: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1629,7 +1609,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: .9</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1659,12 +1639,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 4</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 9</t>
+          <t>L105: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1694,12 +1674,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: i</t>
+          <t>L59: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 105</t>
+          <t>L107: isolated marker/symbol line :: .3</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1729,12 +1709,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L65: symbol-only separator/garbage line :: 66-67</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 116</t>
+          <t>L109: symbol-only separator/garbage line :: 3-4</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1764,12 +1744,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: S.</t>
+          <t>L63: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 107</t>
+          <t>L111: isolated marker/symbol line :: - 8</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1799,12 +1779,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L68: symbol-only separator/garbage line :: . 68</t>
+          <t>L65: symbol-only separator/garbage line :: 66-67</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: . 107</t>
+          <t>L112: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1834,12 +1814,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L69: symbol-only separator/garbage line :: . 67-68</t>
+          <t>L67: isolated marker/symbol line :: S.</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 112</t>
+          <t>L114: symbol-only separator/garbage line :: 6—87</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1869,12 +1849,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: Â·</t>
+          <t>L68: symbol-only separator/garbage line :: . 68</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 105</t>
+          <t>L115: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1904,12 +1884,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L72: symbol-only separator/garbage line :: . 111</t>
+          <t>L69: symbol-only separator/garbage line :: . 67-68</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: 1</t>
+          <t>L117: isolated marker/symbol line :: .9</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1939,12 +1919,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L71: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 1</t>
+          <t>L118: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1974,12 +1954,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 112</t>
+          <t>L72: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: .2</t>
+          <t>L120: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2009,10 +1989,14 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 8</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr"/>
+          <t>L73: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L122: isolated marker/symbol line :: 116</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2040,10 +2024,14 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 12</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr"/>
+          <t>L74: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2071,10 +2059,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L75: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L125: symbol-only separator/garbage line :: . 107</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2102,10 +2094,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 105</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L77: isolated marker/symbol line :: 12</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L127: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2133,10 +2129,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 116</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L85: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L139: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2164,10 +2164,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 105</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L90: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L141: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2195,10 +2199,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L91: isolated marker/symbol line :: 116</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L143: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2226,10 +2234,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: . 2</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L92: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L146: symbol-only separator/garbage line :: 79—80—81</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2257,10 +2269,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L93: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L148: symbol-only separator/garbage line :: . 82—83</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2288,10 +2304,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L96: symbol-only separator/garbage line :: 5-6</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L94: isolated marker/symbol line :: . 2</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: .2</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2319,10 +2339,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L152: symbol-only separator/garbage line :: 5—6</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2350,7 +2374,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 9</t>
+          <t>L96: symbol-only separator/garbage line :: 5-6</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2381,7 +2405,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 107</t>
+          <t>L98: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2412,7 +2436,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 107</t>
+          <t>L100: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2443,7 +2467,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 112</t>
+          <t>L101: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2474,7 +2498,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: )</t>
+          <t>L102: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2505,7 +2529,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 79-80-81</t>
+          <t>L103: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2536,7 +2560,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: 82-83</t>
+          <t>L108: isolated marker/symbol line :: )</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2551,6 +2575,68 @@
       <c r="X51" s="1" t="inlineStr"/>
       <c r="Y51" s="1" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L109: symbol-only separator/garbage line :: 79-80-81</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L111: symbol-only separator/garbage line :: 82-83</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
